--- a/data/raw/inventory/Week 7/White_Mulberry/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 7/White_Mulberry/Inventory Snapshot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 7\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17127ADA-0E38-472E-9769-3E5635E12648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6CA385-0FFD-46D8-9824-C176241DFAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -610,16 +610,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1115,7 +1112,7 @@
       <c r="C3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>118</v>
       </c>
       <c r="I3" s="1">
@@ -1124,10 +1121,10 @@
       <c r="J3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="K3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1138,7 +1135,7 @@
       <c r="C4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I4" s="1">
@@ -1147,10 +1144,10 @@
       <c r="J4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="3" t="s">
+      <c r="K4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1161,7 +1158,7 @@
       <c r="C5" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>126</v>
       </c>
       <c r="I5" s="1">
@@ -1170,10 +1167,10 @@
       <c r="J5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="3" t="s">
+      <c r="K5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1184,7 +1181,7 @@
       <c r="C6" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>127</v>
       </c>
       <c r="I6" s="1">
@@ -1193,10 +1190,10 @@
       <c r="J6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="3" t="s">
+      <c r="K6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1207,7 +1204,7 @@
       <c r="C7" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>128</v>
       </c>
       <c r="I7" s="1">
@@ -1216,10 +1213,10 @@
       <c r="J7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="3" t="s">
+      <c r="K7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1230,7 +1227,7 @@
       <c r="C8" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>129</v>
       </c>
       <c r="I8" s="1">
@@ -1239,10 +1236,10 @@
       <c r="J8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8" s="3" t="s">
+      <c r="K8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1253,7 +1250,7 @@
       <c r="C9" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>130</v>
       </c>
       <c r="I9" s="1">
@@ -1262,10 +1259,10 @@
       <c r="J9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L9" s="3" t="s">
+      <c r="K9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1276,7 +1273,7 @@
       <c r="C10" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>146</v>
       </c>
       <c r="I10" s="1">
@@ -1285,10 +1282,10 @@
       <c r="J10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L10" s="3" t="s">
+      <c r="K10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1299,7 +1296,7 @@
       <c r="C11" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>61</v>
       </c>
       <c r="I11" s="1">
@@ -1308,10 +1305,10 @@
       <c r="J11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L11" s="3" t="s">
+      <c r="K11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1322,7 +1319,7 @@
       <c r="C12" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>73</v>
       </c>
       <c r="I12" s="1">
@@ -1331,10 +1328,10 @@
       <c r="J12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L12" s="3" t="s">
+      <c r="K12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1345,7 +1342,7 @@
       <c r="C13" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>76</v>
       </c>
       <c r="I13" s="1">
@@ -1354,10 +1351,10 @@
       <c r="J13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L13" s="3" t="s">
+      <c r="K13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1368,7 +1365,7 @@
       <c r="C14" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>147</v>
       </c>
       <c r="I14" s="1">
@@ -1377,10 +1374,10 @@
       <c r="J14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="K14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1391,7 +1388,7 @@
       <c r="C15" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="1" t="s">
         <v>103</v>
       </c>
       <c r="I15" s="1">
@@ -1400,10 +1397,10 @@
       <c r="J15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L15" s="3" t="s">
+      <c r="K15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1414,7 +1411,7 @@
       <c r="C16" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>148</v>
       </c>
       <c r="I16" s="1">
@@ -1423,10 +1420,10 @@
       <c r="J16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L16" s="3" t="s">
+      <c r="K16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1437,7 +1434,7 @@
       <c r="C17" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>102</v>
       </c>
       <c r="I17" s="1">
@@ -1446,10 +1443,10 @@
       <c r="J17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L17" s="3" t="s">
+      <c r="K17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1460,7 +1457,7 @@
       <c r="C18" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="1" t="s">
         <v>78</v>
       </c>
       <c r="I18" s="1">
@@ -1469,10 +1466,10 @@
       <c r="J18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L18" s="3" t="s">
+      <c r="K18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1483,7 +1480,7 @@
       <c r="C19" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="1" t="s">
         <v>82</v>
       </c>
       <c r="I19" s="1">
@@ -1492,10 +1489,10 @@
       <c r="J19" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L19" s="3" t="s">
+      <c r="K19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1506,7 +1503,7 @@
       <c r="C20" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="1" t="s">
         <v>149</v>
       </c>
       <c r="I20" s="1">
@@ -1515,10 +1512,10 @@
       <c r="J20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L20" s="3" t="s">
+      <c r="K20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1529,7 +1526,7 @@
       <c r="C21" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="1" t="s">
         <v>121</v>
       </c>
       <c r="I21" s="1">
@@ -1538,10 +1535,10 @@
       <c r="J21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L21" s="3" t="s">
+      <c r="K21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1552,7 +1549,7 @@
       <c r="C22" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="1" t="s">
         <v>60</v>
       </c>
       <c r="I22" s="1">
@@ -1561,10 +1558,10 @@
       <c r="J22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L22" s="3" t="s">
+      <c r="K22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1575,7 +1572,7 @@
       <c r="C23" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I23" s="1">
@@ -1584,10 +1581,10 @@
       <c r="J23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L23" s="3" t="s">
+      <c r="K23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1598,7 +1595,7 @@
       <c r="C24" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="1" t="s">
         <v>81</v>
       </c>
       <c r="I24" s="1">
@@ -1607,10 +1604,10 @@
       <c r="J24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L24" s="3" t="s">
+      <c r="K24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1621,7 +1618,7 @@
       <c r="C25" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="1" t="s">
         <v>69</v>
       </c>
       <c r="I25" s="1">
@@ -1630,10 +1627,10 @@
       <c r="J25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L25" s="3" t="s">
+      <c r="K25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1644,7 +1641,7 @@
       <c r="C26" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I26" s="1">
@@ -1653,10 +1650,10 @@
       <c r="J26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L26" s="3" t="s">
+      <c r="K26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1667,7 +1664,7 @@
       <c r="C27" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="1" t="s">
         <v>117</v>
       </c>
       <c r="I27" s="1">
@@ -1676,10 +1673,10 @@
       <c r="J27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L27" s="3" t="s">
+      <c r="K27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1690,7 +1687,7 @@
       <c r="C28" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="1" t="s">
         <v>119</v>
       </c>
       <c r="I28" s="1">
@@ -1699,10 +1696,10 @@
       <c r="J28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L28" s="3" t="s">
+      <c r="K28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1713,7 +1710,7 @@
       <c r="C29" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I29" s="1">
@@ -1722,10 +1719,10 @@
       <c r="J29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L29" s="3" t="s">
+      <c r="K29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1736,7 +1733,7 @@
       <c r="C30" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="1" t="s">
         <v>127</v>
       </c>
       <c r="I30" s="1">
@@ -1745,10 +1742,10 @@
       <c r="J30" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L30" s="3" t="s">
+      <c r="K30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1759,7 +1756,7 @@
       <c r="C31" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="1" t="s">
         <v>129</v>
       </c>
       <c r="I31" s="1">
@@ -1768,10 +1765,10 @@
       <c r="J31" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L31" s="3" t="s">
+      <c r="K31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1782,7 +1779,7 @@
       <c r="C32" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="1" t="s">
         <v>63</v>
       </c>
       <c r="I32" s="1">
@@ -1791,10 +1788,10 @@
       <c r="J32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L32" s="3" t="s">
+      <c r="K32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1805,7 +1802,7 @@
       <c r="C33" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="1" t="s">
         <v>64</v>
       </c>
       <c r="I33" s="1">
@@ -1814,10 +1811,10 @@
       <c r="J33" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L33" s="3" t="s">
+      <c r="K33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1828,7 +1825,7 @@
       <c r="C34" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="1" t="s">
         <v>131</v>
       </c>
       <c r="I34" s="1">
@@ -1837,10 +1834,10 @@
       <c r="J34" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L34" s="3" t="s">
+      <c r="K34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L34" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1851,7 +1848,7 @@
       <c r="C35" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="1" t="s">
         <v>132</v>
       </c>
       <c r="I35" s="1">
@@ -1860,10 +1857,10 @@
       <c r="J35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L35" s="3" t="s">
+      <c r="K35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L35" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1874,7 +1871,7 @@
       <c r="C36" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="1" t="s">
         <v>133</v>
       </c>
       <c r="I36" s="1">
@@ -1883,10 +1880,10 @@
       <c r="J36" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K36" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L36" s="3" t="s">
+      <c r="K36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L36" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1897,7 +1894,7 @@
       <c r="C37" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="1" t="s">
         <v>124</v>
       </c>
       <c r="I37" s="1">
@@ -1906,10 +1903,10 @@
       <c r="J37" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L37" s="3" t="s">
+      <c r="K37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1920,7 +1917,7 @@
       <c r="C38" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="1" t="s">
         <v>120</v>
       </c>
       <c r="I38" s="1">
@@ -1929,10 +1926,10 @@
       <c r="J38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L38" s="3" t="s">
+      <c r="K38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L38" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1943,7 +1940,7 @@
       <c r="C39" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="1" t="s">
         <v>121</v>
       </c>
       <c r="I39" s="1">
@@ -1952,10 +1949,10 @@
       <c r="J39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K39" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L39" s="3" t="s">
+      <c r="K39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L39" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1966,7 +1963,7 @@
       <c r="C40" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="1" t="s">
         <v>122</v>
       </c>
       <c r="I40" s="1">
@@ -1975,10 +1972,10 @@
       <c r="J40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L40" s="3" t="s">
+      <c r="K40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1989,7 +1986,7 @@
       <c r="C41" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="1" t="s">
         <v>123</v>
       </c>
       <c r="I41" s="1">
@@ -1998,10 +1995,10 @@
       <c r="J41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L41" s="3" t="s">
+      <c r="K41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L41" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2012,7 +2009,7 @@
       <c r="C42" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="1" t="s">
         <v>62</v>
       </c>
       <c r="I42" s="1">
@@ -2021,10 +2018,10 @@
       <c r="J42" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L42" s="3" t="s">
+      <c r="K42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L42" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2035,7 +2032,7 @@
       <c r="C43" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="1" t="s">
         <v>92</v>
       </c>
       <c r="I43" s="1">
@@ -2044,10 +2041,10 @@
       <c r="J43" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L43" s="3" t="s">
+      <c r="K43" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2058,19 +2055,19 @@
       <c r="C44" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="1" t="s">
         <v>116</v>
       </c>
       <c r="I44" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L44" s="3" t="s">
+      <c r="K44" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2081,19 +2078,20 @@
       <c r="C45" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="1" t="s">
         <v>117</v>
       </c>
       <c r="I45" s="1">
-        <v>80</v>
+        <f>80-35</f>
+        <v>45</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L45" s="3" t="s">
+      <c r="K45" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L45" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2104,7 +2102,7 @@
       <c r="C46" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="1" t="s">
         <v>118</v>
       </c>
       <c r="I46" s="1">
@@ -2113,10 +2111,10 @@
       <c r="J46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L46" s="3" t="s">
+      <c r="K46" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L46" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2127,19 +2125,20 @@
       <c r="C47" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="1" t="s">
         <v>119</v>
       </c>
       <c r="I47" s="1">
-        <v>80</v>
+        <f>80-35</f>
+        <v>45</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L47" s="3" t="s">
+      <c r="K47" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L47" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2150,19 +2149,20 @@
       <c r="C48" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I48" s="1">
-        <v>120</v>
+        <f>120-55</f>
+        <v>65</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L48" s="3" t="s">
+      <c r="K48" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L48" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       <c r="C49" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="1" t="s">
         <v>126</v>
       </c>
       <c r="I49" s="1">
@@ -2182,10 +2182,10 @@
       <c r="J49" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L49" s="3" t="s">
+      <c r="K49" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L49" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       <c r="C50" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="1" t="s">
         <v>127</v>
       </c>
       <c r="I50" s="1">
@@ -2205,10 +2205,10 @@
       <c r="J50" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L50" s="3" t="s">
+      <c r="K50" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L50" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       <c r="C51" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="1" t="s">
         <v>128</v>
       </c>
       <c r="I51" s="1">
@@ -2228,10 +2228,10 @@
       <c r="J51" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K51" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L51" s="3" t="s">
+      <c r="K51" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L51" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       <c r="C52" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="1" t="s">
         <v>130</v>
       </c>
       <c r="I52" s="1">
@@ -2251,10 +2251,10 @@
       <c r="J52" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L52" s="3" t="s">
+      <c r="K52" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L52" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       <c r="C53" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="1" t="s">
         <v>161</v>
       </c>
       <c r="I53" s="1">
@@ -2274,10 +2274,10 @@
       <c r="J53" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K53" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L53" s="3" t="s">
+      <c r="K53" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L53" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       <c r="C54" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="1" t="s">
         <v>149</v>
       </c>
       <c r="I54" s="1">
@@ -2297,10 +2297,10 @@
       <c r="J54" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L54" s="3" t="s">
+      <c r="K54" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L54" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       <c r="C55" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I55" s="1">
@@ -2320,10 +2320,10 @@
       <c r="J55" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L55" s="3" t="s">
+      <c r="K55" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L55" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       <c r="C56" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" s="1" t="s">
         <v>151</v>
       </c>
       <c r="I56" s="1">
@@ -2343,10 +2343,10 @@
       <c r="J56" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L56" s="3" t="s">
+      <c r="K56" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L56" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2357,19 +2357,20 @@
       <c r="C57" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="1" t="s">
         <v>152</v>
       </c>
       <c r="I57" s="1">
-        <v>203</v>
+        <f>203-90</f>
+        <v>113</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L57" s="3" t="s">
+      <c r="K57" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L57" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2380,7 +2381,7 @@
       <c r="C58" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="1" t="s">
         <v>153</v>
       </c>
       <c r="I58" s="1">
@@ -2389,10 +2390,10 @@
       <c r="J58" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L58" s="3" t="s">
+      <c r="K58" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L58" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2403,7 +2404,7 @@
       <c r="C59" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="1" t="s">
         <v>154</v>
       </c>
       <c r="I59" s="1">
@@ -2412,10 +2413,10 @@
       <c r="J59" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L59" s="3" t="s">
+      <c r="K59" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L59" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2426,19 +2427,20 @@
       <c r="C60" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" s="1" t="s">
         <v>146</v>
       </c>
       <c r="I60" s="1">
-        <v>361</v>
+        <f>361-180</f>
+        <v>181</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L60" s="3" t="s">
+      <c r="K60" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L60" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2449,7 +2451,7 @@
       <c r="C61" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="1" t="s">
         <v>155</v>
       </c>
       <c r="I61" s="1">
@@ -2458,10 +2460,10 @@
       <c r="J61" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L61" s="3" t="s">
+      <c r="K61" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L61" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2472,7 +2474,7 @@
       <c r="C62" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="1" t="s">
         <v>156</v>
       </c>
       <c r="I62" s="1">
@@ -2481,10 +2483,10 @@
       <c r="J62" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L62" s="3" t="s">
+      <c r="K62" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L62" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2495,7 +2497,7 @@
       <c r="C63" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="1" t="s">
         <v>157</v>
       </c>
       <c r="I63" s="1">
@@ -2504,10 +2506,10 @@
       <c r="J63" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K63" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L63" s="3" t="s">
+      <c r="K63" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L63" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2524,10 +2526,10 @@
       <c r="J64" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K64" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L64" s="3" t="s">
+      <c r="K64" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L64" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2544,10 +2546,10 @@
       <c r="J65" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K65" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L65" s="3" t="s">
+      <c r="K65" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L65" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2564,10 +2566,10 @@
       <c r="J66" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K66" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L66" s="3" t="s">
+      <c r="K66" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L66" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2584,10 +2586,10 @@
       <c r="J67" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K67" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L67" s="3" t="s">
+      <c r="K67" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L67" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2604,10 +2606,10 @@
       <c r="J68" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K68" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L68" s="3" t="s">
+      <c r="K68" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L68" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2624,10 +2626,10 @@
       <c r="J69" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K69" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L69" s="3" t="s">
+      <c r="K69" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2644,10 +2646,10 @@
       <c r="J70" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K70" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L70" s="3" t="s">
+      <c r="K70" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L70" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2664,10 +2666,10 @@
       <c r="J71" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K71" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L71" s="3" t="s">
+      <c r="K71" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L71" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2684,10 +2686,10 @@
       <c r="J72" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K72" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L72" s="3" t="s">
+      <c r="K72" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L72" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2704,10 +2706,10 @@
       <c r="J73" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K73" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L73" s="3" t="s">
+      <c r="K73" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L73" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2724,10 +2726,10 @@
       <c r="J74" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K74" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L74" s="3" t="s">
+      <c r="K74" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L74" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2744,10 +2746,10 @@
       <c r="J75" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K75" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L75" s="3" t="s">
+      <c r="K75" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L75" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2764,10 +2766,10 @@
       <c r="J76" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K76" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L76" s="3" t="s">
+      <c r="K76" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L76" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2784,10 +2786,10 @@
       <c r="J77" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K77" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L77" s="3" t="s">
+      <c r="K77" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L77" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2804,10 +2806,10 @@
       <c r="J78" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K78" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L78" s="3" t="s">
+      <c r="K78" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L78" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2824,10 +2826,10 @@
       <c r="J79" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K79" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L79" s="3" t="s">
+      <c r="K79" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L79" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2844,10 +2846,10 @@
       <c r="J80" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K80" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L80" s="3" t="s">
+      <c r="K80" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L80" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2864,10 +2866,10 @@
       <c r="J81" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K81" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L81" s="3" t="s">
+      <c r="K81" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L81" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2884,10 +2886,10 @@
       <c r="J82" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K82" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L82" s="3" t="s">
+      <c r="K82" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L82" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2904,10 +2906,10 @@
       <c r="J83" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K83" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L83" s="3" t="s">
+      <c r="K83" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L83" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2924,10 +2926,10 @@
       <c r="J84" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K84" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L84" s="3" t="s">
+      <c r="K84" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L84" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2944,10 +2946,10 @@
       <c r="J85" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K85" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L85" s="3" t="s">
+      <c r="K85" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L85" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2964,10 +2966,10 @@
       <c r="J86" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K86" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L86" s="3" t="s">
+      <c r="K86" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L86" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2984,10 +2986,10 @@
       <c r="J87" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K87" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L87" s="3" t="s">
+      <c r="K87" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L87" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3004,10 +3006,10 @@
       <c r="J88" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K88" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L88" s="3" t="s">
+      <c r="K88" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L88" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3024,10 +3026,10 @@
       <c r="J89" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K89" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L89" s="3" t="s">
+      <c r="K89" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3044,10 +3046,10 @@
       <c r="J90" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K90" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L90" s="3" t="s">
+      <c r="K90" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L90" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3064,10 +3066,10 @@
       <c r="J91" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K91" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L91" s="3" t="s">
+      <c r="K91" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L91" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3084,10 +3086,10 @@
       <c r="J92" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K92" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L92" s="3" t="s">
+      <c r="K92" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L92" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3104,10 +3106,10 @@
       <c r="J93" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K93" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L93" s="3" t="s">
+      <c r="K93" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L93" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3124,10 +3126,10 @@
       <c r="J94" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K94" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L94" s="3" t="s">
+      <c r="K94" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L94" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3144,10 +3146,10 @@
       <c r="J95" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K95" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L95" s="3" t="s">
+      <c r="K95" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L95" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3164,10 +3166,10 @@
       <c r="J96" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K96" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L96" s="3" t="s">
+      <c r="K96" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L96" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3184,10 +3186,10 @@
       <c r="J97" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K97" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L97" s="3" t="s">
+      <c r="K97" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L97" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3204,10 +3206,10 @@
       <c r="J98" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K98" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L98" s="3" t="s">
+      <c r="K98" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L98" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3224,10 +3226,10 @@
       <c r="J99" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K99" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L99" s="3" t="s">
+      <c r="K99" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L99" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3244,10 +3246,10 @@
       <c r="J100" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K100" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L100" s="3" t="s">
+      <c r="K100" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L100" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3264,10 +3266,10 @@
       <c r="J101" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K101" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L101" s="3" t="s">
+      <c r="K101" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L101" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3284,10 +3286,10 @@
       <c r="J102" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K102" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L102" s="3" t="s">
+      <c r="K102" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L102" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3304,10 +3306,10 @@
       <c r="J103" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K103" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L103" s="3" t="s">
+      <c r="K103" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L103" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3324,10 +3326,10 @@
       <c r="J104" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K104" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L104" s="3" t="s">
+      <c r="K104" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L104" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3344,10 +3346,10 @@
       <c r="J105" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K105" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L105" s="3" t="s">
+      <c r="K105" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L105" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3364,10 +3366,10 @@
       <c r="J106" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K106" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L106" s="3" t="s">
+      <c r="K106" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L106" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3384,10 +3386,10 @@
       <c r="J107" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K107" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L107" s="3" t="s">
+      <c r="K107" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L107" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3404,10 +3406,10 @@
       <c r="J108" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K108" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L108" s="3" t="s">
+      <c r="K108" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L108" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3424,10 +3426,10 @@
       <c r="J109" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K109" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L109" s="3" t="s">
+      <c r="K109" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L109" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3444,10 +3446,10 @@
       <c r="J110" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K110" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L110" s="3" t="s">
+      <c r="K110" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L110" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3464,10 +3466,10 @@
       <c r="J111" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K111" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L111" s="3" t="s">
+      <c r="K111" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L111" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3484,10 +3486,10 @@
       <c r="J112" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K112" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L112" s="3" t="s">
+      <c r="K112" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L112" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3504,10 +3506,10 @@
       <c r="J113" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K113" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L113" s="3" t="s">
+      <c r="K113" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L113" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3524,10 +3526,10 @@
       <c r="J114" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K114" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L114" s="3" t="s">
+      <c r="K114" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L114" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3544,10 +3546,10 @@
       <c r="J115" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K115" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L115" s="3" t="s">
+      <c r="K115" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L115" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3564,10 +3566,10 @@
       <c r="J116" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K116" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L116" s="3" t="s">
+      <c r="K116" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L116" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3584,10 +3586,10 @@
       <c r="J117" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K117" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L117" s="3" t="s">
+      <c r="K117" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L117" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3604,10 +3606,10 @@
       <c r="J118" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K118" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L118" s="3" t="s">
+      <c r="K118" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L118" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3624,10 +3626,10 @@
       <c r="J119" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K119" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L119" s="3" t="s">
+      <c r="K119" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L119" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3644,10 +3646,10 @@
       <c r="J120" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K120" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L120" s="3" t="s">
+      <c r="K120" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L120" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3664,10 +3666,10 @@
       <c r="J121" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K121" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L121" s="3" t="s">
+      <c r="K121" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L121" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3684,10 +3686,10 @@
       <c r="J122" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K122" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L122" s="3" t="s">
+      <c r="K122" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L122" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3704,10 +3706,10 @@
       <c r="J123" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K123" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L123" s="3" t="s">
+      <c r="K123" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L123" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3724,10 +3726,10 @@
       <c r="J124" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K124" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L124" s="3" t="s">
+      <c r="K124" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L124" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3744,10 +3746,10 @@
       <c r="J125" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K125" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L125" s="3" t="s">
+      <c r="K125" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L125" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3764,10 +3766,10 @@
       <c r="J126" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K126" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L126" s="3" t="s">
+      <c r="K126" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L126" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3784,10 +3786,10 @@
       <c r="J127" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K127" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L127" s="3" t="s">
+      <c r="K127" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L127" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3804,10 +3806,10 @@
       <c r="J128" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K128" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L128" s="3" t="s">
+      <c r="K128" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L128" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3824,10 +3826,10 @@
       <c r="J129" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K129" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L129" s="3" t="s">
+      <c r="K129" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L129" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3844,10 +3846,10 @@
       <c r="J130" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K130" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L130" s="3" t="s">
+      <c r="K130" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L130" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3864,10 +3866,10 @@
       <c r="J131" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K131" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L131" s="3" t="s">
+      <c r="K131" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L131" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3884,10 +3886,10 @@
       <c r="J132" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K132" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L132" s="3" t="s">
+      <c r="K132" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L132" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3904,10 +3906,10 @@
       <c r="J133" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K133" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L133" s="3" t="s">
+      <c r="K133" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L133" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3924,10 +3926,10 @@
       <c r="J134" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K134" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L134" s="3" t="s">
+      <c r="K134" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L134" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3944,10 +3946,10 @@
       <c r="J135" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K135" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L135" s="3" t="s">
+      <c r="K135" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L135" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3964,10 +3966,10 @@
       <c r="J136" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K136" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L136" s="3" t="s">
+      <c r="K136" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L136" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3984,10 +3986,10 @@
       <c r="J137" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K137" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L137" s="3" t="s">
+      <c r="K137" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L137" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4004,10 +4006,10 @@
       <c r="J138" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K138" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L138" s="3" t="s">
+      <c r="K138" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L138" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4024,10 +4026,10 @@
       <c r="J139" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K139" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L139" s="3" t="s">
+      <c r="K139" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L139" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4044,10 +4046,10 @@
       <c r="J140" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K140" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L140" s="3" t="s">
+      <c r="K140" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L140" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4064,10 +4066,10 @@
       <c r="J141" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K141" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L141" s="3" t="s">
+      <c r="K141" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L141" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4084,10 +4086,10 @@
       <c r="J142" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K142" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L142" s="3" t="s">
+      <c r="K142" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L142" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4104,10 +4106,10 @@
       <c r="J143" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K143" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L143" s="3" t="s">
+      <c r="K143" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L143" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4124,10 +4126,10 @@
       <c r="J144" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K144" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L144" s="3" t="s">
+      <c r="K144" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L144" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4144,10 +4146,10 @@
       <c r="J145" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K145" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L145" s="3" t="s">
+      <c r="K145" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L145" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4164,10 +4166,10 @@
       <c r="J146" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K146" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L146" s="3" t="s">
+      <c r="K146" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L146" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4184,10 +4186,10 @@
       <c r="J147" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K147" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L147" s="3" t="s">
+      <c r="K147" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L147" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4204,10 +4206,10 @@
       <c r="J148" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="K148" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L148" s="3" t="s">
+      <c r="K148" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L148" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4224,10 +4226,10 @@
       <c r="J149" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="K149" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L149" s="3" t="s">
+      <c r="K149" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L149" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4247,7 +4249,7 @@
       <c r="K150" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L150" s="3" t="s">
+      <c r="L150" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4264,10 +4266,10 @@
       <c r="J151" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="K151" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L151" s="3" t="s">
+      <c r="K151" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L151" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4284,10 +4286,10 @@
       <c r="J152" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="K152" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L152" s="3" t="s">
+      <c r="K152" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L152" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4298,7 +4300,7 @@
       <c r="C153" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D153" s="3" t="s">
+      <c r="D153" s="1" t="s">
         <v>116</v>
       </c>
       <c r="I153" s="1">
@@ -4310,7 +4312,7 @@
       <c r="K153" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L153" s="3" t="s">
+      <c r="L153" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4321,7 +4323,7 @@
       <c r="C154" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D154" s="3" t="s">
+      <c r="D154" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I154" s="1">
@@ -4330,10 +4332,10 @@
       <c r="J154" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K154" s="3" t="s">
+      <c r="K154" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L154" s="3" t="s">
+      <c r="L154" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4344,7 +4346,7 @@
       <c r="C155" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D155" s="3" t="s">
+      <c r="D155" s="1" t="s">
         <v>129</v>
       </c>
       <c r="I155" s="1">
@@ -4353,10 +4355,10 @@
       <c r="J155" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K155" s="3" t="s">
+      <c r="K155" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L155" s="3" t="s">
+      <c r="L155" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4367,7 +4369,7 @@
       <c r="C156" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D156" s="3" t="s">
+      <c r="D156" s="1" t="s">
         <v>127</v>
       </c>
       <c r="I156" s="1">
@@ -4376,10 +4378,10 @@
       <c r="J156" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K156" s="3" t="s">
+      <c r="K156" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L156" s="3" t="s">
+      <c r="L156" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4390,7 +4392,7 @@
       <c r="C157" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D157" s="3" t="s">
+      <c r="D157" s="1" t="s">
         <v>126</v>
       </c>
       <c r="I157" s="1">
@@ -4399,10 +4401,10 @@
       <c r="J157" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K157" s="3" t="s">
+      <c r="K157" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L157" s="3" t="s">
+      <c r="L157" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4413,16 +4415,16 @@
       <c r="C158" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="D158" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J158" s="3" t="s">
+      <c r="J158" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K158" s="3" t="s">
+      <c r="K158" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L158" s="3" t="s">
+      <c r="L158" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4433,19 +4435,19 @@
       <c r="C159" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="D159" s="1" t="s">
         <v>130</v>
       </c>
       <c r="I159" s="1">
         <v>24</v>
       </c>
-      <c r="J159" s="3" t="s">
+      <c r="J159" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K159" s="3" t="s">
+      <c r="K159" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L159" s="3" t="s">
+      <c r="L159" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4456,16 +4458,16 @@
       <c r="C160" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D160" s="3" t="s">
+      <c r="D160" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J160" s="3" t="s">
+      <c r="J160" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K160" s="3" t="s">
+      <c r="K160" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L160" s="3" t="s">
+      <c r="L160" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4476,19 +4478,19 @@
       <c r="C161" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D161" s="3" t="s">
+      <c r="D161" s="1" t="s">
         <v>119</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="3" t="s">
+      <c r="J161" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K161" s="3" t="s">
+      <c r="K161" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L161" s="3" t="s">
+      <c r="L161" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4505,10 +4507,10 @@
       <c r="J162" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K162" s="4" t="s">
+      <c r="K162" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L162" s="3" t="s">
+      <c r="L162" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4522,13 +4524,13 @@
       <c r="I163" s="1">
         <v>1</v>
       </c>
-      <c r="J163" s="3" t="s">
+      <c r="J163" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K163" s="4" t="s">
+      <c r="K163" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L163" s="3" t="s">
+      <c r="L163" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4542,13 +4544,13 @@
       <c r="I164" s="1">
         <v>5</v>
       </c>
-      <c r="J164" s="3" t="s">
+      <c r="J164" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K164" s="4" t="s">
+      <c r="K164" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L164" s="3" t="s">
+      <c r="L164" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4562,13 +4564,13 @@
       <c r="I165" s="1">
         <v>7</v>
       </c>
-      <c r="J165" s="3" t="s">
+      <c r="J165" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K165" s="4" t="s">
+      <c r="K165" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L165" s="3" t="s">
+      <c r="L165" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4582,13 +4584,13 @@
       <c r="I166" s="1">
         <v>7</v>
       </c>
-      <c r="J166" s="3" t="s">
+      <c r="J166" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K166" s="4" t="s">
+      <c r="K166" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L166" s="3" t="s">
+      <c r="L166" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4602,13 +4604,13 @@
       <c r="I167" s="1">
         <v>3</v>
       </c>
-      <c r="J167" s="3" t="s">
+      <c r="J167" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K167" s="4" t="s">
+      <c r="K167" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L167" s="3" t="s">
+      <c r="L167" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4622,18 +4624,17 @@
       <c r="I168" s="1">
         <v>3</v>
       </c>
-      <c r="J168" s="3" t="s">
+      <c r="J168" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K168" s="4" t="s">
+      <c r="K168" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L168" s="3" t="s">
+      <c r="L168" s="1" t="s">
         <v>162</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L168" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="6" priority="207"/>
   </conditionalFormatting>
